--- a/data/trans_dic/P17G_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P17G_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha acudido a un médico de la seguridad social en su última visita</t>
+          <t>Población que consultó en las últimas 2 semanas a un/a médico/a de la seguridad social (tasa de respuesta: 99,14%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>63,93; 84,17</t>
+          <t>62,47; 83,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>68,94; 90,2</t>
+          <t>71,19; 89,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66,85; 84,31</t>
+          <t>67,08; 84,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>66,11; 82,89</t>
+          <t>66,82; 83,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,21; 91,02</t>
+          <t>74,74; 91,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,19; 88,45</t>
+          <t>69,08; 88,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,57; 89,68</t>
+          <t>72,4; 89,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>64,52; 78,95</t>
+          <t>65,58; 78,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>71,01; 85,6</t>
+          <t>71,54; 85,45</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>73,72; 87,19</t>
+          <t>73,27; 86,2</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>72,9; 84,82</t>
+          <t>72,86; 85,19</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>68,31; 79,12</t>
+          <t>68,27; 79,09</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>78,3; 95,32</t>
+          <t>79,39; 95,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>66,65; 85,65</t>
+          <t>67,94; 86,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72,74; 89,46</t>
+          <t>73,28; 89,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70,29; 86,9</t>
+          <t>70,91; 86,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>81,23; 94,64</t>
+          <t>80,8; 94,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,59; 95,95</t>
+          <t>80,27; 95,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,17; 94,53</t>
+          <t>82,1; 94,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>71,22; 85,02</t>
+          <t>71,21; 85,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>83,01; 93,37</t>
+          <t>82,9; 93,64</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>76,41; 88,61</t>
+          <t>76,95; 89,07</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80,32; 90,28</t>
+          <t>80,21; 90,6</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>73,27; 84,5</t>
+          <t>73,25; 84,29</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>84,38; 95,27</t>
+          <t>83,86; 95,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>95,04; 99,42</t>
+          <t>94,97; 99,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89,61; 98,05</t>
+          <t>90,52; 98,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>93,06; 99,8</t>
+          <t>93,29; 99,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>82,34; 97,66</t>
+          <t>82,23; 98,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>88,03; 97,83</t>
+          <t>87,96; 97,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>84,52; 98,46</t>
+          <t>85,56; 98,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>82,44; 96,14</t>
+          <t>82,62; 96,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>86,49; 94,85</t>
+          <t>86,58; 95,04</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>93,51; 98,41</t>
+          <t>93,89; 98,75</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>90,88; 97,58</t>
+          <t>90,88; 97,62</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>90,94; 97,53</t>
+          <t>91,33; 97,57</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>90,54; 96,37</t>
+          <t>90,66; 96,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>95,42; 99,04</t>
+          <t>95,26; 99,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>91,22; 97,02</t>
+          <t>91,31; 97,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>89,63; 97,15</t>
+          <t>90,05; 97,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>88,86; 95,77</t>
+          <t>89,19; 96,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,53; 100,0</t>
+          <t>97,31; 100,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,94; 97,45</t>
+          <t>92,27; 97,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>90,52; 96,98</t>
+          <t>90,84; 97,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>91,03; 95,56</t>
+          <t>91,02; 95,55</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>96,97; 99,29</t>
+          <t>97,04; 99,17</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>92,66; 96,71</t>
+          <t>92,84; 96,69</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91,99; 96,52</t>
+          <t>91,49; 96,43</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>88,9; 97,94</t>
+          <t>89,02; 97,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>95,76; 100,0</t>
+          <t>96,05; 100,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>91,42; 98,09</t>
+          <t>92,2; 98,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>94,28; 100,0</t>
+          <t>93,46; 100,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>94,45; 99,47</t>
+          <t>93,89; 99,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>97,75; 100,0</t>
+          <t>97,64; 100,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>92,44; 97,85</t>
+          <t>92,63; 97,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>94,27; 98,73</t>
+          <t>94,22; 98,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>93,94; 98,44</t>
+          <t>94,01; 98,47</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>97,8; 99,76</t>
+          <t>97,46; 99,76</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>93,73; 97,64</t>
+          <t>93,69; 97,39</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>95,24; 98,68</t>
+          <t>95,36; 98,79</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>82,21; 100,0</t>
+          <t>83,42; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>67,38; 94,89</t>
+          <t>65,96; 94,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>77,29; 95,97</t>
+          <t>75,29; 95,66</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>36,76; 100,0</t>
+          <t>39,63; 100,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>93,18; 97,39</t>
+          <t>92,76; 97,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>94,25; 98,06</t>
+          <t>93,98; 98,21</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>92,43; 97,44</t>
+          <t>92,0; 97,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>88,65; 96,43</t>
+          <t>88,6; 96,05</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>93,5; 97,35</t>
+          <t>93,28; 97,25</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>92,51; 97,19</t>
+          <t>92,64; 97,25</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>91,57; 96,62</t>
+          <t>91,8; 96,63</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>86,65; 95,83</t>
+          <t>86,86; 95,99</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>88,13; 92,76</t>
+          <t>88,12; 92,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>91,43; 95,04</t>
+          <t>91,1; 95,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>89,0; 93,06</t>
+          <t>89,31; 93,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>86,28; 91,67</t>
+          <t>86,55; 91,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>92,25; 95,2</t>
+          <t>91,97; 95,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,54; 97,06</t>
+          <t>94,47; 96,99</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,04; 95,11</t>
+          <t>92,14; 95,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>88,4; 92,99</t>
+          <t>88,45; 92,96</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>91,12; 93,8</t>
+          <t>91,2; 93,69</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>93,68; 95,78</t>
+          <t>93,68; 95,79</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>91,61; 94,01</t>
+          <t>91,53; 93,97</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>88,4; 91,63</t>
+          <t>88,34; 91,63</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha acudido a un médico de la seguridad social en su última visita</t>
+          <t>Población que consultó en las últimas 2 semanas a un/a médico/a de la seguridad social (tasa de respuesta: 99,14%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>50681; 66719</t>
+          <t>49522; 66134</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>52221; 68319</t>
+          <t>53919; 67770</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>68538; 86438</t>
+          <t>68768; 86826</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>79518; 99708</t>
+          <t>80380; 99937</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>55656; 68256</t>
+          <t>56051; 68300</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>54494; 69661</t>
+          <t>54403; 69323</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>69869; 85161</t>
+          <t>68754; 85107</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>69293; 84793</t>
+          <t>70428; 84707</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>109538; 132055</t>
+          <t>110358; 131823</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>113898; 134704</t>
+          <t>113199; 133172</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>143979; 167506</t>
+          <t>143897; 168242</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>155542; 180145</t>
+          <t>155429; 180077</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>48945; 59588</t>
+          <t>49625; 59642</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>63380; 81444</t>
+          <t>64604; 81948</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67408; 82903</t>
+          <t>67910; 82599</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>63932; 79047</t>
+          <t>64496; 78753</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>79942; 93134</t>
+          <t>79514; 92719</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>72509; 87415</t>
+          <t>73125; 87180</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>75910; 88406</t>
+          <t>76788; 88567</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>64430; 76920</t>
+          <t>64425; 76953</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>133582; 150258</t>
+          <t>133408; 150691</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>142269; 164994</t>
+          <t>143286; 165846</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>149546; 168090</t>
+          <t>149339; 168680</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>132927; 153310</t>
+          <t>132905; 152925</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>99004; 111781</t>
+          <t>98389; 111560</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>146261; 152999</t>
+          <t>146151; 152967</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>137053; 149964</t>
+          <t>138453; 150215</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>80474; 86302</t>
+          <t>80665; 86302</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>48777; 57856</t>
+          <t>48713; 58260</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80186; 89113</t>
+          <t>80119; 89127</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>51213; 59661</t>
+          <t>51846; 59673</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>39387; 45929</t>
+          <t>39473; 45938</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>152714; 167478</t>
+          <t>152883; 167807</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>229085; 241093</t>
+          <t>230009; 241922</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>194070; 208380</t>
+          <t>194064; 208471</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>122088; 130923</t>
+          <t>122608; 130989</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>260352; 277107</t>
+          <t>260700; 276891</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>282029; 292722</t>
+          <t>281546; 292686</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>263675; 280457</t>
+          <t>263956; 281039</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>194779; 211116</t>
+          <t>195687; 211595</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>197689; 213069</t>
+          <t>198427; 213625</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>241149; 247265</t>
+          <t>240623; 247265</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>243843; 258456</t>
+          <t>244703; 258588</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>172328; 184617</t>
+          <t>172926; 184699</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>464260; 487348</t>
+          <t>464218; 487319</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>526399; 538944</t>
+          <t>526772; 538340</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>513615; 536059</t>
+          <t>514608; 535913</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>375043; 393508</t>
+          <t>372991; 393143</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>72156; 79494</t>
+          <t>72256; 79524</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>103601; 108191</t>
+          <t>103918; 108191</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>148945; 159812</t>
+          <t>150202; 160772</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>83911; 89006</t>
+          <t>83183; 89006</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>188272; 198265</t>
+          <t>187141; 197731</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>268916; 275099</t>
+          <t>268605; 275099</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>242418; 256606</t>
+          <t>242921; 256406</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>253281; 265271</t>
+          <t>253146; 265262</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>263514; 276111</t>
+          <t>263696; 276217</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>374853; 382371</t>
+          <t>373541; 382363</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>398494; 415124</t>
+          <t>398330; 414069</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>340657; 352954</t>
+          <t>341082; 353375</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>20602; 25061</t>
+          <t>20905; 25061</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>25211; 35508</t>
+          <t>24681; 35325</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>33769; 41931</t>
+          <t>32894; 41795</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8562; 23289</t>
+          <t>9229; 23289</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>367061; 383653</t>
+          <t>365412; 383388</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>331895; 345334</t>
+          <t>330965; 345857</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>334465; 352591</t>
+          <t>332926; 352444</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>152836; 166250</t>
+          <t>152754; 165597</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>391738; 407895</t>
+          <t>390833; 407471</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>360407; 378636</t>
+          <t>360893; 378853</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>371393; 391846</t>
+          <t>372289; 391915</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>169554; 187519</t>
+          <t>169974; 187838</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>575360; 605644</t>
+          <t>575313; 604940</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>700239; 727891</t>
+          <t>697696; 727819</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>751017; 785293</t>
+          <t>753571; 786816</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>541288; 575072</t>
+          <t>542927; 576786</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>967160; 998057</t>
+          <t>964140; 997163</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1073506; 1102051</t>
+          <t>1072622; 1101311</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1047776; 1082789</t>
+          <t>1048900; 1083559</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>775329; 815627</t>
+          <t>775752; 815366</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1550242; 1595722</t>
+          <t>1551538; 1593972</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1781272; 1821164</t>
+          <t>1781115; 1821282</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1815940; 1863477</t>
+          <t>1814372; 1862679</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1329839; 1378497</t>
+          <t>1329068; 1378558</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P17G_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P17G_R-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>75,0%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>62,47; 83,43</t>
+          <t>64,37; 83,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>71,19; 89,47</t>
+          <t>70,1; 89,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>67,08; 84,69</t>
+          <t>67,77; 84,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>66,82; 83,08</t>
+          <t>68,28; 82,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,74; 91,07</t>
+          <t>74,11; 91,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,08; 88,02</t>
+          <t>69,06; 88,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,4; 89,62</t>
+          <t>73,65; 89,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>65,58; 78,87</t>
+          <t>66,1; 79,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>71,54; 85,45</t>
+          <t>72,22; 85,03</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>73,27; 86,2</t>
+          <t>72,92; 86,88</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>72,86; 85,19</t>
+          <t>72,85; 85,49</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>68,27; 79,09</t>
+          <t>69,39; 80,0</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>78,88%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>79,39; 95,41</t>
+          <t>80,12; 95,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>67,94; 86,18</t>
+          <t>66,71; 85,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>73,28; 89,14</t>
+          <t>73,33; 89,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70,91; 86,58</t>
+          <t>69,82; 86,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>80,8; 94,22</t>
+          <t>80,68; 94,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>80,27; 95,69</t>
+          <t>79,14; 95,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>82,1; 94,7</t>
+          <t>81,86; 94,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>71,21; 85,06</t>
+          <t>70,72; 85,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>82,9; 93,64</t>
+          <t>83,68; 93,75</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>76,95; 89,07</t>
+          <t>77,05; 88,64</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80,21; 90,6</t>
+          <t>80,35; 90,59</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>73,25; 84,29</t>
+          <t>72,36; 83,49</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>94,95%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>83,86; 95,08</t>
+          <t>84,33; 95,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>94,97; 99,4</t>
+          <t>94,93; 99,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>90,52; 98,21</t>
+          <t>90,06; 98,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>93,29; 99,8</t>
+          <t>91,27; 99,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>82,23; 98,35</t>
+          <t>82,3; 98,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>87,96; 97,84</t>
+          <t>87,63; 97,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>85,56; 98,48</t>
+          <t>86,43; 100,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>82,62; 96,16</t>
+          <t>83,56; 96,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>86,58; 95,04</t>
+          <t>86,11; 94,93</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>93,89; 98,75</t>
+          <t>93,84; 98,42</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>90,88; 97,62</t>
+          <t>90,82; 97,83</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>91,33; 97,57</t>
+          <t>90,89; 97,47</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,24%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>90,66; 96,29</t>
+          <t>90,59; 96,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>95,26; 99,03</t>
+          <t>94,93; 99,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>91,31; 97,22</t>
+          <t>91,37; 97,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>90,05; 97,37</t>
+          <t>89,04; 96,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,19; 96,02</t>
+          <t>88,59; 95,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,31; 100,0</t>
+          <t>97,3; 100,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,27; 97,5</t>
+          <t>91,92; 97,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>90,84; 97,02</t>
+          <t>91,24; 97,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>91,02; 95,55</t>
+          <t>90,76; 95,62</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>97,04; 99,17</t>
+          <t>96,98; 99,29</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>92,84; 96,69</t>
+          <t>92,53; 96,65</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91,49; 96,43</t>
+          <t>91,6; 96,37</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>96,76%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>89,02; 97,98</t>
+          <t>88,21; 97,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>96,05; 100,0</t>
+          <t>95,71; 100,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>92,2; 98,68</t>
+          <t>92,11; 98,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>93,46; 100,0</t>
+          <t>96,52; 100,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>93,89; 99,2</t>
+          <t>93,83; 99,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>97,64; 100,0</t>
+          <t>97,63; 100,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>92,63; 97,77</t>
+          <t>92,43; 97,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>94,22; 98,73</t>
+          <t>93,01; 97,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>94,01; 98,47</t>
+          <t>93,7; 98,41</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>97,46; 99,76</t>
+          <t>97,81; 99,76</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>93,69; 97,39</t>
+          <t>93,63; 97,65</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>95,36; 98,79</t>
+          <t>94,94; 98,15</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>93,06%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>83,42; 100,0</t>
+          <t>82,21; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>65,96; 94,41</t>
+          <t>63,76; 94,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>75,29; 95,66</t>
+          <t>77,61; 95,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>39,63; 100,0</t>
+          <t>40,72; 100,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>92,76; 97,32</t>
+          <t>93,19; 97,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>93,98; 98,21</t>
+          <t>94,31; 98,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>92,0; 97,4</t>
+          <t>92,47; 97,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>88,6; 96,05</t>
+          <t>89,82; 96,54</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>93,28; 97,25</t>
+          <t>93,18; 97,27</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>92,64; 97,25</t>
+          <t>92,43; 97,2</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>91,8; 96,63</t>
+          <t>91,63; 96,59</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>86,86; 95,99</t>
+          <t>88,11; 96,09</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,66%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>88,12; 92,66</t>
+          <t>87,94; 92,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>91,1; 95,03</t>
+          <t>91,02; 94,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>89,31; 93,25</t>
+          <t>88,97; 93,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>86,55; 91,94</t>
+          <t>86,28; 91,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>91,97; 95,12</t>
+          <t>92,06; 95,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,47; 96,99</t>
+          <t>94,58; 97,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,14; 95,18</t>
+          <t>92,31; 95,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>88,45; 92,96</t>
+          <t>88,17; 91,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>91,2; 93,69</t>
+          <t>91,27; 93,84</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>93,68; 95,79</t>
+          <t>93,63; 95,82</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>91,53; 93,97</t>
+          <t>91,41; 93,8</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>88,34; 91,63</t>
+          <t>87,97; 91,12</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>91131</t>
+          <t>100442</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>77723</t>
+          <t>88432</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>168854</t>
+          <t>188874</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>49522; 66134</t>
+          <t>51025; 66461</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>53919; 67770</t>
+          <t>53096; 68009</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>68768; 86826</t>
+          <t>69480; 86932</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>80380; 99937</t>
+          <t>89754; 108904</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>56051; 68300</t>
+          <t>55580; 68337</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>54403; 69323</t>
+          <t>54389; 69681</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>68754; 85107</t>
+          <t>69938; 84924</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>70428; 84707</t>
+          <t>79578; 96104</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>110358; 131823</t>
+          <t>111408; 131168</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>113199; 133172</t>
+          <t>112668; 134228</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>143897; 168242</t>
+          <t>143876; 168828</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>155429; 180077</t>
+          <t>174735; 201477</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>72281</t>
+          <t>77083</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>71305</t>
+          <t>78705</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>143586</t>
+          <t>155788</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>49625; 59642</t>
+          <t>50081; 59656</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>64604; 81948</t>
+          <t>63438; 81677</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67910; 82599</t>
+          <t>67948; 82996</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>64496; 78753</t>
+          <t>68212; 84492</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>79514; 92719</t>
+          <t>79398; 93180</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>73125; 87180</t>
+          <t>72101; 86668</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>76788; 88567</t>
+          <t>76558; 88651</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>64425; 76953</t>
+          <t>70577; 84960</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>133408; 150691</t>
+          <t>134663; 150862</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>143286; 165846</t>
+          <t>143471; 165044</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>149339; 168680</t>
+          <t>149601; 168663</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>132905; 152925</t>
+          <t>142899; 164887</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>84503</t>
+          <t>94049</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>43390</t>
+          <t>48970</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>127893</t>
+          <t>143019</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>98389; 111560</t>
+          <t>98950; 111632</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>146151; 152967</t>
+          <t>146097; 152981</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>138453; 150215</t>
+          <t>137749; 150360</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>80665; 86302</t>
+          <t>88541; 96211</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>48713; 58260</t>
+          <t>48754; 58072</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80119; 89127</t>
+          <t>79819; 89088</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>51846; 59673</t>
+          <t>52375; 60596</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>39473; 45938</t>
+          <t>44807; 51932</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>152883; 167807</t>
+          <t>152050; 167625</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>230009; 241922</t>
+          <t>229886; 241119</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>194064; 208471</t>
+          <t>193944; 208905</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>122608; 130989</t>
+          <t>136906; 146828</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>205140</t>
+          <t>216985</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>179798</t>
+          <t>204947</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>384937</t>
+          <t>421932</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>260700; 276891</t>
+          <t>260495; 276852</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>281546; 292686</t>
+          <t>280577; 292684</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>263956; 281039</t>
+          <t>264107; 280890</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>195687; 211595</t>
+          <t>205821; 223954</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>198427; 213625</t>
+          <t>197090; 213339</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>240623; 247265</t>
+          <t>240595; 247265</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>244703; 258588</t>
+          <t>243785; 258807</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>172926; 184699</t>
+          <t>197566; 210332</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>464218; 487319</t>
+          <t>462881; 487654</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>526772; 538340</t>
+          <t>526423; 538962</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>514608; 535913</t>
+          <t>512853; 535728</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>372991; 393143</t>
+          <t>410108; 431455</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>88092</t>
+          <t>95149</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>259698</t>
+          <t>208775</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>347791</t>
+          <t>303925</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>72256; 79524</t>
+          <t>71600; 79493</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>103918; 108191</t>
+          <t>103552; 108191</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>150202; 160772</t>
+          <t>150064; 159854</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>83183; 89006</t>
+          <t>92608; 95951</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>187141; 197731</t>
+          <t>187033; 198197</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>268605; 275099</t>
+          <t>268568; 275099</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>242921; 256406</t>
+          <t>242393; 256862</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>253146; 265262</t>
+          <t>202889; 212908</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>263696; 276217</t>
+          <t>262820; 276039</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>373541; 382363</t>
+          <t>374882; 382369</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>398330; 414069</t>
+          <t>398104; 415163</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>341082; 353375</t>
+          <t>298192; 308285</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20011</t>
+          <t>18357</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>161061</t>
+          <t>182742</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>181072</t>
+          <t>201099</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>20905; 25061</t>
+          <t>20604; 25061</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>24681; 35325</t>
+          <t>23857; 35348</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>32894; 41795</t>
+          <t>33911; 41857</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9229; 23289</t>
+          <t>8721; 21416</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>365412; 383388</t>
+          <t>367100; 383774</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>330965; 345857</t>
+          <t>332124; 345353</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>332926; 352444</t>
+          <t>334624; 353114</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>152754; 165597</t>
+          <t>174863; 187954</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>390833; 407471</t>
+          <t>390427; 407553</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>360893; 378853</t>
+          <t>360098; 378661</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>372289; 391915</t>
+          <t>371604; 391737</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>169974; 187838</t>
+          <t>190415; 207664</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>561158</t>
+          <t>602067</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>792974</t>
+          <t>812571</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1354133</t>
+          <t>1414638</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>575313; 604940</t>
+          <t>574171; 605284</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>697696; 727819</t>
+          <t>697117; 727412</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>753571; 786816</t>
+          <t>750704; 786560</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>542927; 576786</t>
+          <t>582154; 617884</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>964140; 997163</t>
+          <t>965119; 997968</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1072622; 1101311</t>
+          <t>1073880; 1102398</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1048900; 1083559</t>
+          <t>1050905; 1082945</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>775752; 815366</t>
+          <t>796345; 827808</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1551538; 1593972</t>
+          <t>1552686; 1596425</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1781115; 1821282</t>
+          <t>1780174; 1821804</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1814372; 1862679</t>
+          <t>1812027; 1859340</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1329068; 1378558</t>
+          <t>1388095; 1437715</t>
         </is>
       </c>
     </row>
